--- a/metagenomics/metagenomic_viruses.xlsx
+++ b/metagenomics/metagenomic_viruses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdstengl/Google_Drive/Manuscripts/2024_ISV_VT/Tillie_figure_repo/metagenomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F6FF5-9048-2441-9BCE-D2ABE9FD93BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E041174-494C-484E-BCF0-6D111DFC7508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1700" yWindow="1460" windowWidth="32720" windowHeight="17140" xr2:uid="{9462351F-0423-6643-8C2C-5D675EE58685}"/>
   </bookViews>
@@ -53,42 +53,18 @@
     <t>Genbank accession (b)</t>
   </si>
   <si>
-    <t>Average coverage depth (X) (c)</t>
-  </si>
-  <si>
     <t>Poza Rica</t>
   </si>
   <si>
     <t>Aedes anphevirus</t>
   </si>
   <si>
-    <t>38x</t>
-  </si>
-  <si>
-    <t>Verdadero virus RNA 1 &amp; 2</t>
-  </si>
-  <si>
-    <t>356x</t>
-  </si>
-  <si>
-    <t>Chaq-like virus</t>
-  </si>
-  <si>
-    <t>910x</t>
-  </si>
-  <si>
     <t>Guadeloupe mosquito virus RNA 1 &amp; 2</t>
   </si>
   <si>
-    <t>1202x</t>
-  </si>
-  <si>
     <t>Tapachula</t>
   </si>
   <si>
-    <t>589x</t>
-  </si>
-  <si>
     <t>MT742174, MT742175</t>
   </si>
   <si>
@@ -126,6 +102,30 @@
   </si>
   <si>
     <t>PV646271-PV646272</t>
+  </si>
+  <si>
+    <t>verdadero virus RNA 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>chaq-like virus</t>
+  </si>
+  <si>
+    <t>Average coverage depth (×) (c)</t>
+  </si>
+  <si>
+    <t>38×</t>
+  </si>
+  <si>
+    <t>356×</t>
+  </si>
+  <si>
+    <t>910×</t>
+  </si>
+  <si>
+    <t>1202×</t>
+  </si>
+  <si>
+    <t>589×</t>
   </si>
 </sst>
 </file>
@@ -649,107 +649,107 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5">
         <v>99.6</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="D3" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="E6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
